--- a/Results/Study 1/ResNet50/Confusion Matrices.xlsx
+++ b/Results/Study 1/ResNet50/Confusion Matrices.xlsx
@@ -400,10 +400,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>512</v>
+        <v>479</v>
       </c>
       <c r="C2">
-        <v>128</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -411,10 +411,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="C3">
-        <v>496</v>
+        <v>535</v>
       </c>
     </row>
   </sheetData>
@@ -440,10 +440,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C2">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -451,10 +451,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C3">
-        <v>102</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
